--- a/excels/1급_전산회계책_필기.xlsx
+++ b/excels/1급_전산회계책_필기.xlsx
@@ -1637,7 +1637,7 @@
       <c r="C30" t="inlineStr">
         <is>
           <t>주 식 취득시
-(차) 단기매매증권 2,000,000원 (대) 현통예금 2,000,000원</t>
+(차) 단기매매증권 2,000,000원 (대) 보통예금 2,000,000원</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -1649,7 +1649,7 @@
       <c r="E30" t="inlineStr">
         <is>
           <t>제 2기 1월 1일
-(차) 현통예금 1,500,000원 (대) 단 기매매증권 1,000,000원
+(차) 보통예금 1,500,000원 (대) 단기매매증권 1,000,000원
 단기매매증권처분이익 500,000원</t>
         </is>
       </c>
@@ -1891,7 +1891,7 @@
       <c r="C36" t="inlineStr">
         <is>
           <t>주 식 취득시
-(차) 단기매매증권 2,000,000원 (대) 현통예금 2,000,000원</t>
+(차) 단기매매증권 2,000,000원 (대) 보통예금 2,000,000원</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -1903,7 +1903,7 @@
       <c r="E36" t="inlineStr">
         <is>
           <t>제 2기 1월 1일
-(차) 현통예금 1,500,000원 (대) 단 기매매증권 1,000,000원
+(차) 보통예금 1,500,000원 (대) 단기매매증권 1,000,000원
 단기매매증권처분이익 500,000원</t>
         </is>
       </c>
@@ -16064,7 +16064,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>처분이익 : (50주 × 25,000원 (장부가액)) - (50주 × 30,000원 (처분가액)) = 250,000 원 (차) 현금 1,500,000원 (대) 단 기매매증권 1,250,000원 단기매매증권처분이익 250,000원 A사 주식 단기매매증권평가이익 100,000원 + 배당금수익 60,000원 = 160,000원</t>
+          <t>처분이익 : (50주 × 25,000원 (장부가액)) - (50주 × 30,000원 (처분가액)) = 250,000 원 (차) 현금 1,500,000원 (대) 단기매매증권 1,250,000원 단기매매증권처분이익 250,000원 A사 주식 단기매매증권평가이익 100,000원 + 배당금수익 60,000원 = 160,000원</t>
         </is>
       </c>
     </row>
@@ -16424,7 +16424,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>처분이익 : (50주 × 25,000원 (장부가액)) - (50주 × 30,000원 (처분가액)) = 250,000 원 (차) 현금 1,500,000원 (대) 단 기매매증권 1,250,000원 단기매매증권처분이익 250,000원 A사 주식 단기매매증권평가이익 100,000원 + 배당금수익 60,000원 = 160,000원</t>
+          <t>처분이익 : (50주 × 25,000원 (장부가액)) - (50주 × 30,000원 (처분가액)) = 250,000 원 (차) 현금 1,500,000원 (대) 단기매매증권 1,250,000원 단기매매증권처분이익 250,000원 A사 주식 단기매매증권평가이익 100,000원 + 배당금수익 60,000원 = 160,000원</t>
         </is>
       </c>
     </row>
@@ -16509,12 +16509,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>개별법은 재고자산의 단가결정방법이다.</t>
+          <t>처분이익 = (50주 × 30,000원 (처분가액)) - (50주 × 25,000원 (장부가액)) = 250,000원. 올바른 분개: (차) 보통예금 1,500,000원 / (대) 단기매매증권 1,250,000원, 단기매매증권처분이익 250,000원 (보기 3번은 취득원가 20,000원을 기준으로 장부가 100만원을 제거하고 처분이익 50만원을 계상하여 틀렸습니다.)</t>
         </is>
       </c>
     </row>

--- a/excels/1급_전산회계책_필기.xlsx
+++ b/excels/1급_전산회계책_필기.xlsx
@@ -11763,7 +11763,11 @@
       <c r="B36" t="n">
         <v>3</v>
       </c>
-      <c r="C36" t="inlineStr"/>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>[답] 1번. 매출채권에 대한 대손충당금 환입액은 대손상각비(판매비와관리비)의 차감계정으로 처리합니다. 기타채권의 환입은 영업외수익입니다.</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -12773,7 +12777,11 @@
       <c r="B114" t="n">
         <v>3</v>
       </c>
-      <c r="C114" t="inlineStr"/>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>[답] 3번. 주식할인발행차금은 자본조정 항목으로 재무상태표와 자본변동표에서 확인할 수 있습니다. 이익잉여금처분계산서에는 이익잉여금 관련 항목만 표시됩니다.</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
@@ -12990,7 +12998,14 @@
       <c r="B131" t="n">
         <v>3</v>
       </c>
-      <c r="C131" t="inlineStr"/>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>[답] 3번. 
+매출총이익 = 매출액 2,000,000 - 매출원가 900,000 = 1,100,000
+영업이익 = 매출총이익 1,100,000 - 판관비(급여 300,000 + 임차료 50,000) = 750,000
+당기순이익 = 영업이익 750,000 - 영업외비용(기부금 30,000 + 재해손실 70,000) = 650,000</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
